--- a/PICHINCHA/Junio/PICHINCHA-JUNIO.xlsx
+++ b/PICHINCHA/Junio/PICHINCHA-JUNIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PICHINCHA\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64F0504-C32A-4FE3-AE69-BFF09242D11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F7546A-B778-49EE-82E9-E79E7BCC4CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$A$1:$O$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$12</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="90">
   <si>
     <t>UF</t>
   </si>
@@ -235,9 +235,6 @@
     <t>AYSA</t>
   </si>
   <si>
-    <t>FLOW - INTERNET CAMARA</t>
-  </si>
-  <si>
     <t>VTO</t>
   </si>
   <si>
@@ -286,24 +283,6 @@
     <t>METROGAS</t>
   </si>
   <si>
-    <t>tsg y flow a ajustar - repetimos montos</t>
-  </si>
-  <si>
-    <t>CERRRAJERIA - ARREGLO CERRADURA PORTON</t>
-  </si>
-  <si>
-    <t>SALVATIERRA MATIAS - DESOBSTRUCCION COLECTORA CLOACAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERRETERIA V&amp;A </t>
-  </si>
-  <si>
-    <t>ARBA - CUOTA 2</t>
-  </si>
-  <si>
-    <t>SERVISUR - CAMBIO DE FOTCELULA - MANO DE OBRA Y MATERIAL</t>
-  </si>
-  <si>
     <t>Vto. 14/07</t>
   </si>
   <si>
@@ -311,6 +290,15 @@
   </si>
   <si>
     <t>TSG - MES DE JUNIO</t>
+  </si>
+  <si>
+    <t>FERRETERIA V&amp;A - PICO MANGUERA</t>
+  </si>
+  <si>
+    <t>FLOW - INTERNET CAMARA - AJUSTE ABONO</t>
+  </si>
+  <si>
+    <t>ARBA</t>
   </si>
 </sst>
 </file>
@@ -323,7 +311,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,13 +412,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1277,7 +1258,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1493,7 +1474,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1576,11 +1556,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1948,7 +1927,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2000,10 +1979,10 @@
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
       <c r="E7" s="24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2026,33 +2005,32 @@
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="136" t="s">
+      <c r="E11" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="136"/>
+      <c r="F11" s="135"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
         <v>67</v>
       </c>
       <c r="B12" s="108"/>
-      <c r="C12" s="131">
-        <v>78921.33</v>
+      <c r="C12" s="165">
+        <v>32956.589999999997</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="56" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="57">
-        <f>-1484152</f>
-        <v>-1484152</v>
+        <v>-735887.07199646719</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="167">
+      <c r="C13" s="165">
         <v>92086</v>
       </c>
       <c r="D13" s="43"/>
@@ -2061,7 +2039,7 @@
       </c>
       <c r="F13" s="59">
         <f>'prorrateo '!F10</f>
-        <v>856053.07200353278</v>
+        <v>564150.37439999986</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2079,48 +2057,49 @@
         <v>20</v>
       </c>
       <c r="F14" s="59">
-        <f>-(C38)</f>
-        <v>-535928.1</v>
+        <f>-(C37)</f>
+        <v>-373926.22</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C15" s="130">
-        <v>39299</v>
+        <f>100100-39299.8</f>
+        <v>60800.2</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F15" s="59">
         <f>-EDESUR!E7</f>
-        <v>-196109.41</v>
+        <v>-196908.95</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" s="130">
-        <v>70904.02</v>
+        <v>71233.279999999999</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F16" s="59">
         <f>EDESUR!E24</f>
-        <v>648604.22600000002</v>
+        <v>205464.27000000002</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="170">
-        <v>5000</v>
+        <v>86</v>
+      </c>
+      <c r="C17" s="130">
+        <v>12287</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
@@ -2128,277 +2107,258 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="130">
-        <v>12287</v>
-      </c>
-      <c r="D18" s="5"/>
+        <v>89</v>
+      </c>
+      <c r="C18" s="130"/>
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="130">
-        <v>6317.6</v>
-      </c>
-      <c r="E19" s="58"/>
-      <c r="F19" s="59"/>
-      <c r="H19" s="122" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="32"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="87">
-        <f>SUM(C12:C19)</f>
-        <v>338414.95</v>
-      </c>
-      <c r="E20" s="60" t="s">
+      <c r="H18" s="108"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="32"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="87">
+        <f>SUM(C12:C18)</f>
+        <v>302963.06999999995</v>
+      </c>
+      <c r="E19" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="121">
-        <f>SUM(F12:F19)</f>
-        <v>-711532.21199646709</v>
-      </c>
+      <c r="F19" s="121">
+        <f>SUM(F12:F18)</f>
+        <v>-537107.59759646724</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="113"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="113"/>
+      <c r="A21" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="35"/>
+      <c r="C21" s="130">
+        <f>65203*5%+65203</f>
+        <v>68463.149999999994</v>
+      </c>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="35"/>
+        <v>87</v>
+      </c>
       <c r="C22" s="130">
-        <f>65203*5%+65203</f>
-        <v>68463.149999999994</v>
+        <v>2500</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
-        <v>86</v>
-      </c>
+      <c r="A23" s="31"/>
       <c r="B23" s="35"/>
-      <c r="C23" s="130">
-        <v>40000</v>
-      </c>
+      <c r="C23" s="130"/>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
-        <v>90</v>
-      </c>
+    <row r="24" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="31"/>
       <c r="B24" s="35"/>
-      <c r="C24" s="130">
-        <f>25000+7500</f>
-        <v>32500</v>
-      </c>
+      <c r="C24" s="130"/>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="B25" s="35"/>
-      <c r="C25" s="130">
-        <v>56550</v>
+      <c r="C25" s="112">
+        <f>550928.1-373926.22</f>
+        <v>177001.88</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="112">
-        <v>0</v>
+      <c r="A26" s="32"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="109">
+        <f>SUM(C20:C25)</f>
+        <v>247965.03</v>
       </c>
       <c r="D26" s="5"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="6"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="32"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="109">
-        <f>SUM(C21:C26)</f>
-        <v>197513.15</v>
+      <c r="A27" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49">
+        <f>+C26+C19</f>
+        <v>550928.1</v>
       </c>
       <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="49">
-        <f>+C27+C20</f>
-        <v>535928.1</v>
-      </c>
-      <c r="D28" s="5"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="82"/>
+      <c r="C28" s="83"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="69" t="s">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="82"/>
-      <c r="C29" s="83"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
     </row>
     <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
-        <v>24</v>
-      </c>
+      <c r="A30" s="44"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="54"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="44"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="54"/>
+      <c r="A31" s="52"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="53">
+        <v>0</v>
+      </c>
       <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="52"/>
-      <c r="B32" s="51"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="62"/>
       <c r="C32" s="53">
         <v>0</v>
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="61"/>
-      <c r="B33" s="62"/>
-      <c r="C33" s="53">
-        <v>0</v>
-      </c>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="78"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="81"/>
       <c r="F33" s="6"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="78"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="81"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="86"/>
       <c r="F34" s="6"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="86"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="81">
+        <v>0</v>
+      </c>
       <c r="F35" s="6"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="78"/>
-      <c r="B36" s="84"/>
-      <c r="C36" s="81">
-        <v>0</v>
-      </c>
-      <c r="F36" s="6"/>
+      <c r="A36" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="64"/>
+      <c r="C36" s="65">
+        <f>SUM(C31:C35)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="64"/>
-      <c r="C37" s="65">
-        <f>SUM(C32:C36)</f>
-        <v>0</v>
-      </c>
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="53">
+        <f>C27-C25</f>
+        <v>373926.22</v>
+      </c>
+      <c r="F37" s="6"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="53">
-        <f>C28-C26</f>
-        <v>535928.1</v>
+      <c r="A38" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="77">
+        <f>+C27</f>
+        <v>550928.1</v>
       </c>
       <c r="F38" s="6"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="77">
-        <f>+C28</f>
-        <v>535928.1</v>
-      </c>
-      <c r="F39" s="6"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="63" t="s">
+      <c r="A39" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="65">
-        <f>+C28+C37</f>
-        <v>535928.1</v>
-      </c>
-      <c r="E40" s="16"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="65">
+        <f>+C27+C36</f>
+        <v>550928.1</v>
+      </c>
+      <c r="E39" s="16"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D44" s="6"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D45" s="6"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
+      <c r="B46" s="136"/>
+      <c r="C46" s="136"/>
+      <c r="D46" s="136"/>
+      <c r="E46" s="136"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="137"/>
-      <c r="C47" s="137"/>
-      <c r="D47" s="137"/>
-      <c r="E47" s="137"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="137"/>
-      <c r="C48" s="137"/>
-      <c r="D48" s="137"/>
-      <c r="E48" s="137"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="137"/>
-      <c r="C49" s="137"/>
-      <c r="D49" s="137"/>
-      <c r="E49" s="137"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="19"/>
+      <c r="B48" s="136"/>
+      <c r="C48" s="136"/>
+      <c r="D48" s="136"/>
+      <c r="E48" s="136"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="19"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="20"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="18"/>
       <c r="B61" s="18"/>
-      <c r="C61" s="20"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C61" s="18"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
@@ -2418,15 +2378,10 @@
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="18"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B47:E49"/>
+    <mergeCell ref="B46:E48"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2538,10 +2493,10 @@
         <v>38</v>
       </c>
       <c r="L3" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -2575,7 +2530,7 @@
         <v>Vto. 14/07</v>
       </c>
       <c r="M4" s="66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -2590,11 +2545,11 @@
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="41">
-        <v>86036.752000000008</v>
+        <v>114593.04479999999</v>
       </c>
       <c r="F5" s="80">
         <f>E5</f>
-        <v>86036.752000000008</v>
+        <v>114593.04479999999</v>
       </c>
       <c r="G5" s="67">
         <f>E5-F5</f>
@@ -2636,11 +2591,11 @@
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="41">
-        <v>86036.752000000008</v>
+        <v>110185.62</v>
       </c>
       <c r="F6" s="80">
         <f>E6</f>
-        <v>86036.752000000008</v>
+        <v>110185.62</v>
       </c>
       <c r="G6" s="67">
         <f t="shared" ref="G6:G9" si="0">E6-F6</f>
@@ -2682,11 +2637,11 @@
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="41">
-        <v>159545.88224000001</v>
+        <v>114593.04479999999</v>
       </c>
       <c r="F7" s="80">
         <f t="shared" ref="F7:F8" si="5">E7</f>
-        <v>159545.88224000001</v>
+        <v>114593.04479999999</v>
       </c>
       <c r="G7" s="67">
         <f t="shared" si="0"/>
@@ -2728,11 +2683,11 @@
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="41">
-        <v>438396.93376353284</v>
+        <v>114593.04479999999</v>
       </c>
       <c r="F8" s="80">
         <f t="shared" si="5"/>
-        <v>438396.93376353284</v>
+        <v>114593.04479999999</v>
       </c>
       <c r="G8" s="67">
         <f t="shared" si="0"/>
@@ -2774,11 +2729,11 @@
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="41">
-        <v>86036.752000000008</v>
+        <v>110185.62</v>
       </c>
       <c r="F9" s="80">
         <f>E9</f>
-        <v>86036.752000000008</v>
+        <v>110185.62</v>
       </c>
       <c r="G9" s="67">
         <f t="shared" si="0"/>
@@ -2820,11 +2775,11 @@
       </c>
       <c r="E10" s="42">
         <f t="shared" si="6"/>
-        <v>856053.07200353278</v>
+        <v>564150.37439999986</v>
       </c>
       <c r="F10" s="42">
         <f t="shared" si="6"/>
-        <v>856053.07200353278</v>
+        <v>564150.37439999986</v>
       </c>
       <c r="G10" s="50">
         <f t="shared" si="6"/>
@@ -2856,70 +2811,70 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="138"/>
-      <c r="B11" s="138"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="138"/>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
-      <c r="J11" s="138"/>
-      <c r="K11" s="138"/>
-      <c r="L11" s="138"/>
-      <c r="M11" s="138"/>
+      <c r="A11" s="137"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
     </row>
     <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="139"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="139"/>
-      <c r="G13" s="139"/>
-      <c r="H13" s="139"/>
-      <c r="I13" s="139"/>
-      <c r="J13" s="139"/>
-      <c r="K13" s="139"/>
-      <c r="L13" s="139"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="138"/>
+      <c r="G13" s="138"/>
+      <c r="H13" s="138"/>
+      <c r="I13" s="138"/>
+      <c r="J13" s="138"/>
+      <c r="K13" s="138"/>
+      <c r="L13" s="138"/>
     </row>
     <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="139"/>
-      <c r="D14" s="139"/>
-      <c r="E14" s="139"/>
-      <c r="F14" s="139"/>
-      <c r="G14" s="139"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="139"/>
-      <c r="J14" s="139"/>
-      <c r="K14" s="139"/>
-      <c r="L14" s="139"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
     </row>
     <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="139"/>
-      <c r="D15" s="139"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="139"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="139"/>
-      <c r="K15" s="139"/>
-      <c r="L15" s="139"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="138"/>
+      <c r="J15" s="138"/>
+      <c r="K15" s="138"/>
+      <c r="L15" s="138"/>
     </row>
     <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="139"/>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="139"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="139"/>
-      <c r="J16" s="139"/>
-      <c r="K16" s="139"/>
-      <c r="L16" s="139"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="138"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="138"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2968,21 +2923,21 @@
       <c r="A3"/>
       <c r="B3"/>
       <c r="K3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M3" s="6">
         <f>E6</f>
-        <v>59261.97</v>
+        <v>59706.1</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="B4"/>
       <c r="C4" s="124" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" s="124"/>
-      <c r="E4" s="169">
+      <c r="E4" s="166">
         <v>79470.880000000005</v>
       </c>
       <c r="G4" t="s">
@@ -2995,33 +2950,33 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O4" s="120">
         <f>M3-K8</f>
-        <v>-23231.479999999996</v>
+        <v>-22787.35</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5" s="33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" s="33"/>
-      <c r="E5" s="166">
-        <v>57376.56</v>
+      <c r="E5" s="167">
+        <v>57731.97</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6" s="108" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D6" s="108"/>
       <c r="E6" s="168">
-        <v>59261.97</v>
+        <v>59706.1</v>
       </c>
       <c r="G6" s="124">
         <v>1</v>
@@ -3041,11 +2996,11 @@
       </c>
       <c r="L6" s="126">
         <f>O$4/5</f>
-        <v>-4646.2959999999994</v>
-      </c>
-      <c r="N6" s="133">
+        <v>-4557.4699999999993</v>
+      </c>
+      <c r="N6" s="132">
         <f>SUM(K6:M6)</f>
-        <v>35089.144</v>
+        <v>35177.97</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3055,7 +3010,7 @@
       <c r="D7" s="122"/>
       <c r="E7" s="123">
         <f>SUM(E4:E6)</f>
-        <v>196109.41</v>
+        <v>196908.95</v>
       </c>
       <c r="G7" s="125">
         <v>2</v>
@@ -3071,15 +3026,15 @@
       </c>
       <c r="K7" s="120">
         <f>E5/2</f>
-        <v>28688.28</v>
+        <v>28865.985000000001</v>
       </c>
       <c r="L7" s="126">
         <f>O$4/5</f>
-        <v>-4646.2959999999994</v>
-      </c>
-      <c r="N7" s="134">
+        <v>-4557.4699999999993</v>
+      </c>
+      <c r="N7" s="133">
         <f t="shared" ref="N7:N10" si="0">SUM(K7:M7)</f>
-        <v>24041.984</v>
+        <v>24308.514999999999</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3102,11 +3057,11 @@
       </c>
       <c r="L8" s="126">
         <f t="shared" ref="L8:L11" si="1">O$4/5</f>
-        <v>-4646.2959999999994</v>
-      </c>
-      <c r="N8" s="134">
+        <v>-4557.4699999999993</v>
+      </c>
+      <c r="N8" s="133">
         <f t="shared" si="0"/>
-        <v>77847.153999999995</v>
+        <v>77935.98</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3126,15 +3081,15 @@
       </c>
       <c r="K9" s="120">
         <f>E5/2</f>
-        <v>28688.28</v>
+        <v>28865.985000000001</v>
       </c>
       <c r="L9" s="126">
         <f t="shared" si="1"/>
-        <v>-4646.2959999999994</v>
-      </c>
-      <c r="N9" s="134">
+        <v>-4557.4699999999993</v>
+      </c>
+      <c r="N9" s="133">
         <f t="shared" si="0"/>
-        <v>24041.984</v>
+        <v>24308.514999999999</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3158,11 +3113,11 @@
       </c>
       <c r="L10" s="126">
         <f t="shared" si="1"/>
-        <v>-4646.2959999999994</v>
-      </c>
-      <c r="N10" s="135">
+        <v>-4557.4699999999993</v>
+      </c>
+      <c r="N10" s="134">
         <f t="shared" si="0"/>
-        <v>35089.144</v>
+        <v>35177.97</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -3170,7 +3125,7 @@
       <c r="B11"/>
       <c r="L11" s="126">
         <f t="shared" si="1"/>
-        <v>-4646.2959999999994</v>
+        <v>-4557.4699999999993</v>
       </c>
       <c r="N11" s="127"/>
     </row>
@@ -3183,7 +3138,7 @@
       <c r="A13"/>
       <c r="B13"/>
       <c r="C13" s="129" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D13" s="129"/>
       <c r="E13" s="129"/>
@@ -3202,7 +3157,7 @@
       <c r="B14"/>
       <c r="N14" s="128">
         <f>SUM(N6:N13)</f>
-        <v>196109.41</v>
+        <v>196908.94999999998</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -3212,119 +3167,119 @@
     <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="3:10" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C17" s="119" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="119" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="119" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="119" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="143" t="s">
-        <v>82</v>
-      </c>
-      <c r="I17" s="144"/>
-      <c r="J17" s="145"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="144"/>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" s="120">
-        <v>199078.77000000002</v>
-      </c>
-      <c r="E18" s="132">
+        <v>27583.722000000002</v>
+      </c>
+      <c r="E18" s="131">
         <f>C18</f>
-        <v>199078.77000000002</v>
+        <v>27583.722000000002</v>
       </c>
       <c r="F18" s="6">
         <f>N6</f>
-        <v>35089.144</v>
-      </c>
-      <c r="H18" s="146">
+        <v>35177.97</v>
+      </c>
+      <c r="H18" s="145">
         <f>C18-E18+F18</f>
-        <v>35089.144</v>
-      </c>
-      <c r="I18" s="147"/>
-      <c r="J18" s="148"/>
+        <v>35177.97</v>
+      </c>
+      <c r="I18" s="146"/>
+      <c r="J18" s="147"/>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="120">
-        <v>131973.81400000001</v>
-      </c>
-      <c r="E19" s="132">
-        <f>C19</f>
-        <v>131973.81400000001</v>
+        <v>35812.577000000005</v>
+      </c>
+      <c r="E19" s="131">
+        <f t="shared" ref="E19:E22" si="2">C19</f>
+        <v>35812.577000000005</v>
       </c>
       <c r="F19" s="6">
         <f>N7</f>
-        <v>24041.984</v>
-      </c>
-      <c r="H19" s="146">
-        <f t="shared" ref="H19:H22" si="2">C19-E19+F19</f>
-        <v>24041.984</v>
-      </c>
-      <c r="I19" s="147"/>
-      <c r="J19" s="148"/>
+        <v>24308.514999999999</v>
+      </c>
+      <c r="H19" s="145">
+        <f t="shared" ref="H19:H22" si="3">C19-E19+F19</f>
+        <v>24308.514999999999</v>
+      </c>
+      <c r="I19" s="146"/>
+      <c r="J19" s="147"/>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="120">
-        <v>96846.073999999993</v>
-      </c>
-      <c r="E20" s="132">
-        <f t="shared" ref="E20:E21" si="3">C20</f>
-        <v>96846.073999999993</v>
+        <v>78671.671999999991</v>
+      </c>
+      <c r="E20" s="131">
+        <f t="shared" si="2"/>
+        <v>78671.671999999991</v>
       </c>
       <c r="F20" s="6">
         <f t="shared" ref="F20:F22" si="4">N8</f>
-        <v>77847.153999999995</v>
-      </c>
-      <c r="H20" s="146">
+        <v>77935.98</v>
+      </c>
+      <c r="H20" s="145">
         <f>C20-E20+F20</f>
-        <v>77847.153999999995</v>
-      </c>
-      <c r="I20" s="147"/>
-      <c r="J20" s="148"/>
+        <v>77935.98</v>
+      </c>
+      <c r="I20" s="146"/>
+      <c r="J20" s="147"/>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="120">
-        <v>131973.81400000001</v>
-      </c>
-      <c r="E21" s="132">
-        <f t="shared" si="3"/>
-        <v>131973.81400000001</v>
+        <v>35812.577000000005</v>
+      </c>
+      <c r="E21" s="131">
+        <f t="shared" si="2"/>
+        <v>35812.577000000005</v>
       </c>
       <c r="F21" s="6">
         <f>N9</f>
-        <v>24041.984</v>
-      </c>
-      <c r="H21" s="146">
-        <f t="shared" si="2"/>
-        <v>24041.984</v>
-      </c>
-      <c r="I21" s="147"/>
-      <c r="J21" s="148"/>
+        <v>24308.514999999999</v>
+      </c>
+      <c r="H21" s="145">
+        <f t="shared" si="3"/>
+        <v>24308.514999999999</v>
+      </c>
+      <c r="I21" s="146"/>
+      <c r="J21" s="147"/>
     </row>
     <row r="22" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="120">
-        <v>88731.754000000001</v>
-      </c>
-      <c r="E22" s="132">
-        <f>C22</f>
-        <v>88731.754000000001</v>
+        <v>27583.722000000002</v>
+      </c>
+      <c r="E22" s="131">
+        <f t="shared" si="2"/>
+        <v>27583.722000000002</v>
       </c>
       <c r="F22" s="6">
         <f t="shared" si="4"/>
-        <v>35089.144</v>
-      </c>
-      <c r="H22" s="140">
-        <f t="shared" si="2"/>
-        <v>35089.144</v>
-      </c>
-      <c r="I22" s="141"/>
-      <c r="J22" s="142"/>
+        <v>35177.97</v>
+      </c>
+      <c r="H22" s="139">
+        <f t="shared" si="3"/>
+        <v>35177.97</v>
+      </c>
+      <c r="I22" s="140"/>
+      <c r="J22" s="141"/>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="E24" s="6">
         <f>SUM(E18:E23)</f>
-        <v>648604.22600000002</v>
+        <v>205464.27000000002</v>
       </c>
     </row>
   </sheetData>
@@ -3360,60 +3315,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="156"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="155"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="156" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="160">
+      <c r="B2" s="157"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="159">
         <v>565</v>
       </c>
-      <c r="E2" s="161"/>
+      <c r="E2" s="160"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="162" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="162" t="s">
+      <c r="A3" s="161" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="162" t="s">
+      <c r="C3" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="164" t="s">
+      <c r="D3" s="163" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="149" t="s">
+      <c r="E3" s="148" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="149" t="s">
+      <c r="F3" s="148" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="149" t="s">
+      <c r="G3" s="148" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="163"/>
-      <c r="B4" s="163"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="150"/>
+      <c r="A4" s="162"/>
+      <c r="B4" s="162"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="164"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
@@ -3573,11 +3528,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="151"/>
-      <c r="B12" s="152"/>
-      <c r="C12" s="152"/>
-      <c r="D12" s="152"/>
-      <c r="E12" s="153"/>
+      <c r="A12" s="150"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="152"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>
